--- a/EBS pollock/Data/2024_ADMB_estimate.xlsx
+++ b/EBS pollock/Data/2024_ADMB_estimate.xlsx
@@ -1,69 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20416"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\grant.adams\GitHub\Rceattle-models\EBS pollock\Data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13832587-7AE7-494A-B9DB-A238BAD94DFB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="888" yWindow="1452" windowWidth="24648" windowHeight="13380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="2024 SAFE" sheetId="1" r:id="rId1"/>
     <sheet name="Recruitment" sheetId="2" r:id="rId2"/>
     <sheet name="SSB" sheetId="3" r:id="rId3"/>
     <sheet name="Total biomass" sheetId="4" r:id="rId4"/>
+    <sheet name="Biomass" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="7">
-  <si>
-    <t>Year</t>
-  </si>
-  <si>
-    <t>SSB</t>
-  </si>
-  <si>
-    <t>Recruitment</t>
-  </si>
-  <si>
-    <t>Est</t>
-  </si>
-  <si>
-    <t>SD</t>
-  </si>
-  <si>
-    <t>LB</t>
-  </si>
-  <si>
-    <t>UB</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
-      <sz val="12"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -88,29 +53,20 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 6" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
 </styleSheet>
 </file>
 
@@ -125,44 +81,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -189,32 +145,14 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -241,24 +179,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -270,196 +190,214 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AZ70"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C62"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:52" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-    </row>
-    <row r="2" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>SSB</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Recruitment</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2">
         <v>1964</v>
       </c>
       <c r="B2">
-        <v>530.36699999999996</v>
+        <v>530.367</v>
       </c>
       <c r="C2">
         <v>6362.91</v>
       </c>
-      <c r="G2" s="2"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-    </row>
-    <row r="3" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3">
       <c r="A3">
         <v>1965</v>
       </c>
       <c r="B3">
-        <v>621.96900000000005</v>
+        <v>621.9690000000001</v>
       </c>
       <c r="C3">
-        <v>20924.099999999999</v>
-      </c>
-      <c r="G3" s="2"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-    </row>
-    <row r="4" spans="1:52" x14ac:dyDescent="0.3">
+        <v>20924.1</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4">
         <v>1966</v>
       </c>
@@ -469,11 +407,8 @@
       <c r="C4">
         <v>15021.7</v>
       </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-    </row>
-    <row r="5" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5">
       <c r="A5">
         <v>1967</v>
       </c>
@@ -483,11 +418,8 @@
       <c r="C5">
         <v>25464</v>
       </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-    </row>
-    <row r="6" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6">
       <c r="A6">
         <v>1968</v>
       </c>
@@ -497,11 +429,8 @@
       <c r="C6">
         <v>22070.5</v>
       </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-    </row>
-    <row r="7" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7">
       <c r="A7">
         <v>1969</v>
       </c>
@@ -511,11 +440,8 @@
       <c r="C7">
         <v>26095.5</v>
       </c>
-      <c r="F7" s="2"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-    </row>
-    <row r="8" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8">
       <c r="A8">
         <v>1970</v>
       </c>
@@ -525,11 +451,8 @@
       <c r="C8">
         <v>23463.3</v>
       </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-    </row>
-    <row r="9" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9">
       <c r="A9">
         <v>1971</v>
       </c>
@@ -539,11 +462,8 @@
       <c r="C9">
         <v>14389.5</v>
       </c>
-      <c r="G9" s="2"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-    </row>
-    <row r="10" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10">
       <c r="A10">
         <v>1972</v>
       </c>
@@ -553,53 +473,8 @@
       <c r="C10">
         <v>11752.7</v>
       </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
-      <c r="P10" s="2"/>
-      <c r="Q10" s="2"/>
-      <c r="R10" s="2"/>
-      <c r="S10" s="2"/>
-      <c r="T10" s="2"/>
-      <c r="U10" s="2"/>
-      <c r="V10" s="2"/>
-      <c r="W10" s="2"/>
-      <c r="X10" s="2"/>
-      <c r="Y10" s="2"/>
-      <c r="Z10" s="2"/>
-      <c r="AA10" s="2"/>
-      <c r="AB10" s="2"/>
-      <c r="AC10" s="2"/>
-      <c r="AD10" s="2"/>
-      <c r="AE10" s="2"/>
-      <c r="AF10" s="2"/>
-      <c r="AG10" s="2"/>
-      <c r="AH10" s="2"/>
-      <c r="AI10" s="2"/>
-      <c r="AJ10" s="2"/>
-      <c r="AK10" s="2"/>
-      <c r="AL10" s="2"/>
-      <c r="AM10" s="2"/>
-      <c r="AN10" s="2"/>
-      <c r="AO10" s="2"/>
-      <c r="AP10" s="2"/>
-      <c r="AQ10" s="2"/>
-      <c r="AR10" s="2"/>
-      <c r="AS10" s="2"/>
-      <c r="AT10" s="2"/>
-      <c r="AU10" s="2"/>
-      <c r="AV10" s="2"/>
-      <c r="AW10" s="2"/>
-      <c r="AX10" s="2"/>
-      <c r="AY10" s="2"/>
-      <c r="AZ10" s="2"/>
-    </row>
-    <row r="11" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11">
       <c r="A11">
         <v>1973</v>
       </c>
@@ -607,13 +482,10 @@
         <v>1364.05</v>
       </c>
       <c r="C11">
-        <v>26724.400000000001</v>
-      </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-    </row>
-    <row r="12" spans="1:52" x14ac:dyDescent="0.3">
+        <v>26724.4</v>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12">
         <v>1974</v>
       </c>
@@ -623,95 +495,74 @@
       <c r="C12">
         <v>19449.7</v>
       </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-    </row>
-    <row r="13" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13">
       <c r="A13">
         <v>1975</v>
       </c>
       <c r="B13">
-        <v>966.29200000000003</v>
+        <v>966.292</v>
       </c>
       <c r="C13">
         <v>16414</v>
       </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-    </row>
-    <row r="14" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14">
       <c r="A14">
         <v>1976</v>
       </c>
       <c r="B14">
-        <v>926.93899999999996</v>
+        <v>926.939</v>
       </c>
       <c r="C14">
         <v>12615.7</v>
       </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-    </row>
-    <row r="15" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15">
       <c r="A15">
         <v>1977</v>
       </c>
       <c r="B15">
-        <v>1111.1099999999999</v>
+        <v>1111.11</v>
       </c>
       <c r="C15">
         <v>13292</v>
       </c>
-      <c r="G15" s="2"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-    </row>
-    <row r="16" spans="1:52" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16">
       <c r="A16">
         <v>1978</v>
       </c>
       <c r="B16">
-        <v>989.91700000000003</v>
+        <v>989.917</v>
       </c>
       <c r="C16">
         <v>24349.5</v>
       </c>
-      <c r="G16" s="2"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17">
       <c r="A17">
         <v>1979</v>
       </c>
       <c r="B17">
-        <v>906.76099999999997</v>
+        <v>906.761</v>
       </c>
       <c r="C17">
         <v>57027.4</v>
       </c>
-      <c r="G17" s="2"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18">
       <c r="A18">
         <v>1980</v>
       </c>
       <c r="B18">
-        <v>1071.6199999999999</v>
+        <v>1071.62</v>
       </c>
       <c r="C18">
         <v>27259.8</v>
       </c>
-      <c r="G18" s="2"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19">
       <c r="A19">
         <v>1981</v>
       </c>
@@ -721,11 +572,8 @@
       <c r="C19">
         <v>31885.9</v>
       </c>
-      <c r="G19" s="2"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20">
       <c r="A20">
         <v>1982</v>
       </c>
@@ -735,11 +583,8 @@
       <c r="C20">
         <v>18243.5</v>
       </c>
-      <c r="G20" s="2"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21">
       <c r="A21">
         <v>1983</v>
       </c>
@@ -749,11 +594,8 @@
       <c r="C21">
         <v>51081.4</v>
       </c>
-      <c r="G21" s="2"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22">
       <c r="A22">
         <v>1984</v>
       </c>
@@ -763,11 +605,8 @@
       <c r="C22">
         <v>14020.1</v>
       </c>
-      <c r="G22" s="2"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23">
       <c r="A23">
         <v>1985</v>
       </c>
@@ -777,11 +616,8 @@
       <c r="C23">
         <v>32534</v>
       </c>
-      <c r="G23" s="2"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24">
       <c r="A24">
         <v>1986</v>
       </c>
@@ -791,11 +627,8 @@
       <c r="C24">
         <v>12523.6</v>
       </c>
-      <c r="G24" s="2"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25">
       <c r="A25">
         <v>1987</v>
       </c>
@@ -805,11 +638,8 @@
       <c r="C25">
         <v>7072.35</v>
       </c>
-      <c r="G25" s="2"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26">
       <c r="A26">
         <v>1988</v>
       </c>
@@ -819,11 +649,8 @@
       <c r="C26">
         <v>5423.49</v>
       </c>
-      <c r="G26" s="2"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27">
       <c r="A27">
         <v>1989</v>
       </c>
@@ -833,11 +660,8 @@
       <c r="C27">
         <v>11365.5</v>
       </c>
-      <c r="G27" s="2"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28">
       <c r="A28">
         <v>1990</v>
       </c>
@@ -847,11 +671,8 @@
       <c r="C28">
         <v>49400.7</v>
       </c>
-      <c r="G28" s="2"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29">
       <c r="A29">
         <v>1991</v>
       </c>
@@ -859,13 +680,10 @@
         <v>2119.04</v>
       </c>
       <c r="C29">
-        <v>26389.200000000001</v>
-      </c>
-      <c r="G29" s="2"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+        <v>26389.2</v>
+      </c>
+    </row>
+    <row r="30">
       <c r="A30">
         <v>1992</v>
       </c>
@@ -875,11 +693,8 @@
       <c r="C30">
         <v>22654.9</v>
       </c>
-      <c r="G30" s="2"/>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31">
       <c r="A31">
         <v>1993</v>
       </c>
@@ -889,11 +704,8 @@
       <c r="C31">
         <v>44718.5</v>
       </c>
-      <c r="G31" s="2"/>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="32">
       <c r="A32">
         <v>1994</v>
       </c>
@@ -903,11 +715,8 @@
       <c r="C32">
         <v>15205</v>
       </c>
-      <c r="G32" s="2"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="33">
       <c r="A33">
         <v>1995</v>
       </c>
@@ -917,11 +726,8 @@
       <c r="C33">
         <v>10637.6</v>
       </c>
-      <c r="G33" s="2"/>
-      <c r="H33" s="1"/>
-      <c r="I33" s="1"/>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34">
       <c r="A34">
         <v>1996</v>
       </c>
@@ -931,11 +737,8 @@
       <c r="C34">
         <v>22035</v>
       </c>
-      <c r="G34" s="2"/>
-      <c r="H34" s="1"/>
-      <c r="I34" s="1"/>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35">
       <c r="A35">
         <v>1997</v>
       </c>
@@ -945,11 +748,8 @@
       <c r="C35">
         <v>29734.1</v>
       </c>
-      <c r="G35" s="2"/>
-      <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="36">
       <c r="A36">
         <v>1998</v>
       </c>
@@ -959,11 +759,8 @@
       <c r="C36">
         <v>14519.3</v>
       </c>
-      <c r="G36" s="2"/>
-      <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="37">
       <c r="A37">
         <v>1999</v>
       </c>
@@ -973,11 +770,8 @@
       <c r="C37">
         <v>15776.5</v>
       </c>
-      <c r="G37" s="2"/>
-      <c r="H37" s="1"/>
-      <c r="I37" s="1"/>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="38">
       <c r="A38">
         <v>2000</v>
       </c>
@@ -985,13 +779,10 @@
         <v>2722.38</v>
       </c>
       <c r="C38">
-        <v>24285.599999999999</v>
-      </c>
-      <c r="G38" s="2"/>
-      <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+        <v>24285.6</v>
+      </c>
+    </row>
+    <row r="39">
       <c r="A39">
         <v>2001</v>
       </c>
@@ -999,41 +790,32 @@
         <v>2762.51</v>
       </c>
       <c r="C39">
-        <v>34202.400000000001</v>
-      </c>
-      <c r="G39" s="2"/>
-      <c r="H39" s="1"/>
-      <c r="I39" s="1"/>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+        <v>34202.4</v>
+      </c>
+    </row>
+    <row r="40">
       <c r="A40">
         <v>2002</v>
       </c>
       <c r="B40">
-        <v>2566.4299999999998</v>
+        <v>2566.43</v>
       </c>
       <c r="C40">
-        <v>22705.599999999999</v>
-      </c>
-      <c r="G40" s="2"/>
-      <c r="H40" s="1"/>
-      <c r="I40" s="1"/>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+        <v>22705.6</v>
+      </c>
+    </row>
+    <row r="41">
       <c r="A41">
         <v>2003</v>
       </c>
       <c r="B41">
-        <v>2602.8000000000002</v>
+        <v>2602.8</v>
       </c>
       <c r="C41">
         <v>14098.7</v>
       </c>
-      <c r="G41" s="2"/>
-      <c r="H41" s="1"/>
-      <c r="I41" s="1"/>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="42">
       <c r="A42">
         <v>2004</v>
       </c>
@@ -1043,11 +825,8 @@
       <c r="C42">
         <v>6340.16</v>
       </c>
-      <c r="G42" s="2"/>
-      <c r="H42" s="1"/>
-      <c r="I42" s="1"/>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="43">
       <c r="A43">
         <v>2005</v>
       </c>
@@ -1055,13 +834,10 @@
         <v>2551.29</v>
       </c>
       <c r="C43">
-        <v>4462.0200000000004</v>
-      </c>
-      <c r="G43" s="2"/>
-      <c r="H43" s="1"/>
-      <c r="I43" s="1"/>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+        <v>4462.02</v>
+      </c>
+    </row>
+    <row r="44">
       <c r="A44">
         <v>2006</v>
       </c>
@@ -1071,11 +847,8 @@
       <c r="C44">
         <v>11228.4</v>
       </c>
-      <c r="G44" s="2"/>
-      <c r="H44" s="1"/>
-      <c r="I44" s="1"/>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="45">
       <c r="A45">
         <v>2007</v>
       </c>
@@ -1085,11 +858,8 @@
       <c r="C45">
         <v>24504.9</v>
       </c>
-      <c r="G45" s="2"/>
-      <c r="H45" s="1"/>
-      <c r="I45" s="1"/>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="46">
       <c r="A46">
         <v>2008</v>
       </c>
@@ -1099,11 +869,8 @@
       <c r="C46">
         <v>13012.3</v>
       </c>
-      <c r="G46" s="2"/>
-      <c r="H46" s="1"/>
-      <c r="I46" s="1"/>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="47">
       <c r="A47">
         <v>2009</v>
       </c>
@@ -1113,10 +880,8 @@
       <c r="C47">
         <v>48558.2</v>
       </c>
-      <c r="H47" s="1"/>
-      <c r="I47" s="1"/>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="48">
       <c r="A48">
         <v>2010</v>
       </c>
@@ -1124,10 +889,10 @@
         <v>1554.75</v>
       </c>
       <c r="C48">
-        <v>22411.599999999999</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+        <v>22411.6</v>
+      </c>
+    </row>
+    <row r="49">
       <c r="A49">
         <v>2011</v>
       </c>
@@ -1138,18 +903,18 @@
         <v>13623.1</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50">
       <c r="A50">
         <v>2012</v>
       </c>
       <c r="B50">
-        <v>2345.9899999999998</v>
+        <v>2345.99</v>
       </c>
       <c r="C50">
         <v>11795.6</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51">
       <c r="A51">
         <v>2013</v>
       </c>
@@ -1160,18 +925,18 @@
         <v>42753.2</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52">
       <c r="A52">
         <v>2014</v>
       </c>
       <c r="B52">
-        <v>2620.0500000000002</v>
+        <v>2620.05</v>
       </c>
       <c r="C52">
         <v>49038.7</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53">
       <c r="A53">
         <v>2015</v>
       </c>
@@ -1182,7 +947,7 @@
         <v>21229.7</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="54">
       <c r="A54">
         <v>2016</v>
       </c>
@@ -1193,7 +958,7 @@
         <v>8015.08</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="55">
       <c r="A55">
         <v>2017</v>
       </c>
@@ -1204,7 +969,7 @@
         <v>8016.94</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="56">
       <c r="A56">
         <v>2018</v>
       </c>
@@ -1215,7 +980,7 @@
         <v>16501.8</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="57">
       <c r="A57">
         <v>2019</v>
       </c>
@@ -1226,7 +991,7 @@
         <v>81112.7</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="58">
       <c r="A58">
         <v>2020</v>
       </c>
@@ -1237,7 +1002,7 @@
         <v>20413.7</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="59">
       <c r="A59">
         <v>2021</v>
       </c>
@@ -1248,7 +1013,7 @@
         <v>11331.5</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="60">
       <c r="A60">
         <v>2022</v>
       </c>
@@ -1259,7 +1024,7 @@
         <v>11485.8</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="61">
       <c r="A61">
         <v>2023</v>
       </c>
@@ -1267,10 +1032,10 @@
         <v>3333.76</v>
       </c>
       <c r="C61">
-        <v>16759.099999999999</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+        <v>16759.1</v>
+      </c>
+    </row>
+    <row r="62">
       <c r="A62">
         <v>2024</v>
       </c>
@@ -1278,32 +1043,8 @@
         <v>3389.48</v>
       </c>
       <c r="C62">
-        <v>18286.099999999999</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A63" s="1"/>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A64" s="1"/>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A65" s="1"/>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A66" s="1"/>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A67" s="1"/>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A68" s="1"/>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A69" s="1"/>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A70" s="1"/>
+        <v>18286.1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1311,1062 +1052,1072 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C3CC098-F8E2-4D37-ABCD-D1C33B6F7A68}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E62"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Est</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>LB</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>UB</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2">
         <v>1964</v>
       </c>
       <c r="B2">
-        <v>6362.91</v>
+        <v>6368.32</v>
       </c>
       <c r="C2">
-        <v>2402.9</v>
+        <v>2510.6</v>
       </c>
       <c r="D2">
-        <v>3065.56</v>
+        <v>2977.75</v>
       </c>
       <c r="E2">
-        <v>13206.9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+        <v>13619.5</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3">
         <v>1965</v>
       </c>
       <c r="B3">
-        <v>20924.099999999999</v>
+        <v>22410.6</v>
       </c>
       <c r="C3">
-        <v>5238.6099999999997</v>
+        <v>5863.64</v>
       </c>
       <c r="D3">
-        <v>12778.6</v>
+        <v>13395</v>
       </c>
       <c r="E3">
-        <v>34262</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+        <v>37494.3</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4">
         <v>1966</v>
       </c>
       <c r="B4">
-        <v>15021.7</v>
+        <v>16004.1</v>
       </c>
       <c r="C4">
-        <v>4745.13</v>
+        <v>5183.35</v>
       </c>
       <c r="D4">
-        <v>8106.68</v>
+        <v>8509.41</v>
       </c>
       <c r="E4">
-        <v>27835.3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+        <v>30099.6</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5">
         <v>1967</v>
       </c>
       <c r="B5">
-        <v>25464</v>
+        <v>27385.8</v>
       </c>
       <c r="C5">
-        <v>6558.89</v>
+        <v>7123.85</v>
       </c>
       <c r="D5">
-        <v>15338.5</v>
+        <v>16416</v>
       </c>
       <c r="E5">
-        <v>42273.7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+        <v>45685.9</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6">
         <v>1968</v>
       </c>
       <c r="B6">
-        <v>22070.5</v>
+        <v>23152.3</v>
       </c>
       <c r="C6">
-        <v>6192.45</v>
+        <v>6598.11</v>
       </c>
       <c r="D6">
-        <v>12726.5</v>
+        <v>13239.6</v>
       </c>
       <c r="E6">
-        <v>38275</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+        <v>40486.9</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7">
         <v>1969</v>
       </c>
       <c r="B7">
-        <v>26095.5</v>
+        <v>27129.9</v>
       </c>
       <c r="C7">
-        <v>6737.66</v>
+        <v>7089.94</v>
       </c>
       <c r="D7">
-        <v>15700.4</v>
+        <v>16225.4</v>
       </c>
       <c r="E7">
-        <v>43373.1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+        <v>45362.9</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8">
         <v>1970</v>
       </c>
       <c r="B8">
-        <v>23463.3</v>
+        <v>24244.1</v>
       </c>
       <c r="C8">
-        <v>6321.23</v>
+        <v>6591.87</v>
       </c>
       <c r="D8">
-        <v>13818.8</v>
+        <v>14211.4</v>
       </c>
       <c r="E8">
-        <v>39839</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+        <v>41359.3</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9">
         <v>1971</v>
       </c>
       <c r="B9">
-        <v>14389.5</v>
+        <v>14591.2</v>
       </c>
       <c r="C9">
-        <v>4719.1099999999997</v>
+        <v>4863.53</v>
       </c>
       <c r="D9">
-        <v>7593.28</v>
+        <v>7623.71</v>
       </c>
       <c r="E9">
-        <v>27268.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+        <v>27926.6</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10">
         <v>1972</v>
       </c>
       <c r="B10">
-        <v>11752.7</v>
+        <v>11803.5</v>
       </c>
       <c r="C10">
-        <v>3935.23</v>
+        <v>4027.97</v>
       </c>
       <c r="D10">
-        <v>6123.4</v>
+        <v>6077.51</v>
       </c>
       <c r="E10">
-        <v>22557</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+        <v>22924.2</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11">
         <v>1973</v>
       </c>
       <c r="B11">
-        <v>26724.400000000001</v>
+        <v>27731.5</v>
       </c>
       <c r="C11">
-        <v>5048.93</v>
+        <v>5338.61</v>
       </c>
       <c r="D11">
-        <v>18375.8</v>
+        <v>18935.6</v>
       </c>
       <c r="E11">
-        <v>38866.1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+        <v>40613.2</v>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12">
         <v>1974</v>
       </c>
       <c r="B12">
-        <v>19449.7</v>
+        <v>20796</v>
       </c>
       <c r="C12">
-        <v>3788.76</v>
+        <v>4130.66</v>
       </c>
       <c r="D12">
-        <v>13221.7</v>
+        <v>14032</v>
       </c>
       <c r="E12">
-        <v>28611.4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+        <v>30820.5</v>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13">
         <v>1975</v>
       </c>
       <c r="B13">
-        <v>16414</v>
+        <v>18535.9</v>
       </c>
       <c r="C13">
-        <v>2925.09</v>
+        <v>3389.62</v>
       </c>
       <c r="D13">
-        <v>11524.8</v>
+        <v>12896.8</v>
       </c>
       <c r="E13">
-        <v>23377.4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+        <v>26640.7</v>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14">
         <v>1976</v>
       </c>
       <c r="B14">
-        <v>12615.7</v>
+        <v>15041.2</v>
       </c>
       <c r="C14">
-        <v>2114.8000000000002</v>
+        <v>2623.84</v>
       </c>
       <c r="D14">
-        <v>9043.07</v>
+        <v>10638.9</v>
       </c>
       <c r="E14">
-        <v>17599.8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+        <v>21265.1</v>
+      </c>
+    </row>
+    <row r="15">
       <c r="A15">
         <v>1977</v>
       </c>
       <c r="B15">
-        <v>13292</v>
+        <v>16781.6</v>
       </c>
       <c r="C15">
-        <v>1935.14</v>
+        <v>2529.4</v>
       </c>
       <c r="D15">
-        <v>9949.39</v>
+        <v>12435.2</v>
       </c>
       <c r="E15">
-        <v>17757.5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+        <v>22647.3</v>
+      </c>
+    </row>
+    <row r="16">
       <c r="A16">
         <v>1978</v>
       </c>
       <c r="B16">
-        <v>24349.5</v>
+        <v>31748.5</v>
       </c>
       <c r="C16">
-        <v>2353.08</v>
+        <v>3164.89</v>
       </c>
       <c r="D16">
-        <v>20079.2</v>
+        <v>26022.6</v>
       </c>
       <c r="E16">
-        <v>29527.9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+        <v>38734.3</v>
+      </c>
+    </row>
+    <row r="17">
       <c r="A17">
         <v>1979</v>
       </c>
       <c r="B17">
-        <v>57027.4</v>
+        <v>70372.89999999999</v>
       </c>
       <c r="C17">
-        <v>3648.08</v>
+        <v>4682.84</v>
       </c>
       <c r="D17">
-        <v>50185.3</v>
+        <v>61612.8</v>
       </c>
       <c r="E17">
-        <v>64802.400000000001</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+        <v>80378.60000000001</v>
+      </c>
+    </row>
+    <row r="18">
       <c r="A18">
         <v>1980</v>
       </c>
       <c r="B18">
-        <v>27259.8</v>
+        <v>27876.8</v>
       </c>
       <c r="C18">
-        <v>2389.6</v>
+        <v>2500.27</v>
       </c>
       <c r="D18">
-        <v>22883.7</v>
+        <v>23307.4</v>
       </c>
       <c r="E18">
-        <v>32472.6</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+        <v>33341.9</v>
+      </c>
+    </row>
+    <row r="19">
       <c r="A19">
         <v>1981</v>
       </c>
       <c r="B19">
-        <v>31885.9</v>
+        <v>30771.9</v>
       </c>
       <c r="C19">
-        <v>2683.93</v>
+        <v>2758.04</v>
       </c>
       <c r="D19">
-        <v>26953.599999999999</v>
+        <v>25731.1</v>
       </c>
       <c r="E19">
-        <v>37720.9</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+        <v>36800.1</v>
+      </c>
+    </row>
+    <row r="20">
       <c r="A20">
         <v>1982</v>
       </c>
       <c r="B20">
-        <v>18243.5</v>
+        <v>17290.5</v>
       </c>
       <c r="C20">
-        <v>1985.95</v>
+        <v>1890.56</v>
       </c>
       <c r="D20">
-        <v>14683.6</v>
+        <v>13903.3</v>
       </c>
       <c r="E20">
-        <v>22666.400000000001</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+        <v>21503</v>
+      </c>
+    </row>
+    <row r="21">
       <c r="A21">
         <v>1983</v>
       </c>
       <c r="B21">
-        <v>51081.4</v>
+        <v>46666.7</v>
       </c>
       <c r="C21">
-        <v>3139.65</v>
+        <v>3095.68</v>
       </c>
       <c r="D21">
-        <v>45177.9</v>
+        <v>40874.5</v>
       </c>
       <c r="E21">
-        <v>57756.2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+        <v>53279.8</v>
+      </c>
+    </row>
+    <row r="22">
       <c r="A22">
         <v>1984</v>
       </c>
       <c r="B22">
-        <v>14020.1</v>
+        <v>12887.4</v>
       </c>
       <c r="C22">
-        <v>1535.96</v>
+        <v>1463.41</v>
       </c>
       <c r="D22">
-        <v>11268.8</v>
+        <v>10276.6</v>
       </c>
       <c r="E22">
-        <v>17443.2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+        <v>16161.5</v>
+      </c>
+    </row>
+    <row r="23">
       <c r="A23">
         <v>1985</v>
       </c>
       <c r="B23">
-        <v>32534</v>
+        <v>30708.7</v>
       </c>
       <c r="C23">
-        <v>2250.7600000000002</v>
+        <v>2185.37</v>
       </c>
       <c r="D23">
-        <v>28334.7</v>
+        <v>26639.5</v>
       </c>
       <c r="E23">
-        <v>37355.599999999999</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+        <v>35399.4</v>
+      </c>
+    </row>
+    <row r="24">
       <c r="A24">
         <v>1986</v>
       </c>
       <c r="B24">
-        <v>12523.6</v>
+        <v>12178.4</v>
       </c>
       <c r="C24">
-        <v>1264.95</v>
+        <v>1217.49</v>
       </c>
       <c r="D24">
-        <v>10238.1</v>
+        <v>9976.41</v>
       </c>
       <c r="E24">
-        <v>15319.3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+        <v>14866.5</v>
+      </c>
+    </row>
+    <row r="25">
       <c r="A25">
         <v>1987</v>
       </c>
       <c r="B25">
-        <v>7072.35</v>
+        <v>6936.52</v>
       </c>
       <c r="C25">
-        <v>802.4</v>
+        <v>799.064</v>
       </c>
       <c r="D25">
-        <v>5640.69</v>
+        <v>5513.32</v>
       </c>
       <c r="E25">
-        <v>8867.3799999999992</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+        <v>8727.120000000001</v>
+      </c>
+    </row>
+    <row r="26">
       <c r="A26">
         <v>1988</v>
       </c>
       <c r="B26">
-        <v>5423.49</v>
+        <v>5432.5</v>
       </c>
       <c r="C26">
-        <v>621.63599999999997</v>
+        <v>635.457</v>
       </c>
       <c r="D26">
-        <v>4315.66</v>
+        <v>4302.72</v>
       </c>
       <c r="E26">
-        <v>6815.71</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+        <v>6858.93</v>
+      </c>
+    </row>
+    <row r="27">
       <c r="A27">
         <v>1989</v>
       </c>
       <c r="B27">
-        <v>11365.5</v>
+        <v>11554.2</v>
       </c>
       <c r="C27">
-        <v>873.75800000000004</v>
+        <v>912.939</v>
       </c>
       <c r="D27">
-        <v>9747.91</v>
+        <v>9867.690000000001</v>
       </c>
       <c r="E27">
-        <v>13251.5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+        <v>13528.9</v>
+      </c>
+    </row>
+    <row r="28">
       <c r="A28">
         <v>1990</v>
       </c>
       <c r="B28">
-        <v>49400.7</v>
+        <v>50361.9</v>
       </c>
       <c r="C28">
-        <v>1776.19</v>
+        <v>1880.91</v>
       </c>
       <c r="D28">
-        <v>45974.1</v>
+        <v>46738.4</v>
       </c>
       <c r="E28">
-        <v>53082.7</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+        <v>54266.4</v>
+      </c>
+    </row>
+    <row r="29">
       <c r="A29">
         <v>1991</v>
       </c>
       <c r="B29">
-        <v>26389.200000000001</v>
+        <v>26950.6</v>
       </c>
       <c r="C29">
-        <v>1321.88</v>
+        <v>1394.79</v>
       </c>
       <c r="D29">
-        <v>23875.1</v>
+        <v>24302.3</v>
       </c>
       <c r="E29">
-        <v>29168.1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+        <v>29887.6</v>
+      </c>
+    </row>
+    <row r="30">
       <c r="A30">
         <v>1992</v>
       </c>
       <c r="B30">
-        <v>22654.9</v>
+        <v>23155.7</v>
       </c>
       <c r="C30">
-        <v>1259.05</v>
+        <v>1335.65</v>
       </c>
       <c r="D30">
-        <v>20273.400000000001</v>
+        <v>20634.7</v>
       </c>
       <c r="E30">
-        <v>25316.1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+        <v>25984.7</v>
+      </c>
+    </row>
+    <row r="31">
       <c r="A31">
         <v>1993</v>
       </c>
       <c r="B31">
-        <v>44718.5</v>
+        <v>45659.3</v>
       </c>
       <c r="C31">
-        <v>1794.55</v>
+        <v>1941.04</v>
       </c>
       <c r="D31">
-        <v>41271</v>
+        <v>41939.2</v>
       </c>
       <c r="E31">
-        <v>48454</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+        <v>49709.2</v>
+      </c>
+    </row>
+    <row r="32">
       <c r="A32">
         <v>1994</v>
       </c>
       <c r="B32">
-        <v>15205</v>
+        <v>15568.8</v>
       </c>
       <c r="C32">
-        <v>958.77499999999998</v>
+        <v>1007.74</v>
       </c>
       <c r="D32">
-        <v>13405.1</v>
+        <v>13680.1</v>
       </c>
       <c r="E32">
-        <v>17246.599999999999</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+        <v>17718.1</v>
+      </c>
+    </row>
+    <row r="33">
       <c r="A33">
         <v>1995</v>
       </c>
       <c r="B33">
-        <v>10637.6</v>
+        <v>10931.6</v>
       </c>
       <c r="C33">
-        <v>747.51099999999997</v>
+        <v>782.336</v>
       </c>
       <c r="D33">
-        <v>9244.44</v>
+        <v>9475.440000000001</v>
       </c>
       <c r="E33">
-        <v>12240.6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+        <v>12611.4</v>
+      </c>
+    </row>
+    <row r="34">
       <c r="A34">
         <v>1996</v>
       </c>
       <c r="B34">
-        <v>22035</v>
+        <v>22678.5</v>
       </c>
       <c r="C34">
-        <v>1033.82</v>
+        <v>1087.87</v>
       </c>
       <c r="D34">
-        <v>20062.400000000001</v>
+        <v>20605</v>
       </c>
       <c r="E34">
-        <v>24201.5</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+        <v>24960.6</v>
+      </c>
+    </row>
+    <row r="35">
       <c r="A35">
         <v>1997</v>
       </c>
       <c r="B35">
-        <v>29734.1</v>
+        <v>30678.6</v>
       </c>
       <c r="C35">
-        <v>1173.8800000000001</v>
+        <v>1242.48</v>
       </c>
       <c r="D35">
-        <v>27477.5</v>
+        <v>28292.6</v>
       </c>
       <c r="E35">
-        <v>32176.1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+        <v>33265.9</v>
+      </c>
+    </row>
+    <row r="36">
       <c r="A36">
         <v>1998</v>
       </c>
       <c r="B36">
-        <v>14519.3</v>
+        <v>15123.1</v>
       </c>
       <c r="C36">
-        <v>780.48299999999995</v>
+        <v>825.371</v>
       </c>
       <c r="D36">
-        <v>13040.3</v>
+        <v>13560.3</v>
       </c>
       <c r="E36">
-        <v>16166</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+        <v>16865.9</v>
+      </c>
+    </row>
+    <row r="37">
       <c r="A37">
         <v>1999</v>
       </c>
       <c r="B37">
-        <v>15776.5</v>
+        <v>16425.4</v>
       </c>
       <c r="C37">
-        <v>802.56100000000004</v>
+        <v>845.745</v>
       </c>
       <c r="D37">
-        <v>14251.3</v>
+        <v>14819.1</v>
       </c>
       <c r="E37">
-        <v>17465</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+        <v>18205.9</v>
+      </c>
+    </row>
+    <row r="38">
       <c r="A38">
         <v>2000</v>
       </c>
       <c r="B38">
-        <v>24285.599999999999</v>
+        <v>25019.6</v>
       </c>
       <c r="C38">
-        <v>994.04</v>
+        <v>1032.1</v>
       </c>
       <c r="D38">
-        <v>22377.5</v>
+        <v>23039.1</v>
       </c>
       <c r="E38">
-        <v>26356.400000000001</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+        <v>27170.4</v>
+      </c>
+    </row>
+    <row r="39">
       <c r="A39">
         <v>2001</v>
       </c>
       <c r="B39">
-        <v>34202.400000000001</v>
+        <v>34646.7</v>
       </c>
       <c r="C39">
-        <v>1136</v>
+        <v>1169.5</v>
       </c>
       <c r="D39">
-        <v>32004.799999999999</v>
+        <v>32385.5</v>
       </c>
       <c r="E39">
-        <v>36550.9</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+        <v>37065.7</v>
+      </c>
+    </row>
+    <row r="40">
       <c r="A40">
         <v>2002</v>
       </c>
       <c r="B40">
-        <v>22705.599999999999</v>
+        <v>23051.3</v>
       </c>
       <c r="C40">
-        <v>873.08799999999997</v>
+        <v>904.875</v>
       </c>
       <c r="D40">
-        <v>21025.5</v>
+        <v>21311.5</v>
       </c>
       <c r="E40">
-        <v>24520</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+        <v>24933.3</v>
+      </c>
+    </row>
+    <row r="41">
       <c r="A41">
         <v>2003</v>
       </c>
       <c r="B41">
-        <v>14098.7</v>
+        <v>14333.3</v>
       </c>
       <c r="C41">
-        <v>638.529</v>
+        <v>657.8579999999999</v>
       </c>
       <c r="D41">
-        <v>12878.4</v>
+        <v>13076.8</v>
       </c>
       <c r="E41">
-        <v>15434.6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+        <v>15710.5</v>
+      </c>
+    </row>
+    <row r="42">
       <c r="A42">
         <v>2004</v>
       </c>
       <c r="B42">
-        <v>6340.16</v>
+        <v>6333.91</v>
       </c>
       <c r="C42">
-        <v>404.79500000000002</v>
+        <v>403.852</v>
       </c>
       <c r="D42">
-        <v>5580.86</v>
+        <v>5576.31</v>
       </c>
       <c r="E42">
-        <v>7202.78</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+        <v>7194.44</v>
+      </c>
+    </row>
+    <row r="43">
       <c r="A43">
         <v>2005</v>
       </c>
       <c r="B43">
-        <v>4462.0200000000004</v>
+        <v>4368.71</v>
       </c>
       <c r="C43">
-        <v>333.59899999999999</v>
+        <v>329.457</v>
       </c>
       <c r="D43">
-        <v>3843.11</v>
+        <v>3757.88</v>
       </c>
       <c r="E43">
-        <v>5180.6099999999997</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+        <v>5078.82</v>
+      </c>
+    </row>
+    <row r="44">
       <c r="A44">
         <v>2006</v>
       </c>
       <c r="B44">
-        <v>11228.4</v>
+        <v>10761.8</v>
       </c>
       <c r="C44">
-        <v>574.29300000000001</v>
+        <v>544.881</v>
       </c>
       <c r="D44">
-        <v>10137.200000000001</v>
+        <v>9726.02</v>
       </c>
       <c r="E44">
-        <v>12436.9</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+        <v>11907.9</v>
+      </c>
+    </row>
+    <row r="45">
       <c r="A45">
         <v>2007</v>
       </c>
       <c r="B45">
-        <v>24504.9</v>
+        <v>22749.1</v>
       </c>
       <c r="C45">
-        <v>966.15200000000004</v>
+        <v>863.425</v>
       </c>
       <c r="D45">
-        <v>22647.5</v>
+        <v>21086.8</v>
       </c>
       <c r="E45">
-        <v>26514.6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+        <v>24542.6</v>
+      </c>
+    </row>
+    <row r="46">
       <c r="A46">
         <v>2008</v>
       </c>
       <c r="B46">
-        <v>13012.3</v>
+        <v>11347.9</v>
       </c>
       <c r="C46">
-        <v>745.471</v>
+        <v>630.8</v>
       </c>
       <c r="D46">
-        <v>11604.7</v>
+        <v>10154.8</v>
       </c>
       <c r="E46">
-        <v>14590.7</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+        <v>12681.2</v>
+      </c>
+    </row>
+    <row r="47">
       <c r="A47">
         <v>2009</v>
       </c>
       <c r="B47">
-        <v>48558.2</v>
+        <v>42373.3</v>
       </c>
       <c r="C47">
-        <v>1632.08</v>
+        <v>1388.31</v>
       </c>
       <c r="D47">
-        <v>45402.2</v>
+        <v>39686.4</v>
       </c>
       <c r="E47">
-        <v>51933.599999999999</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+        <v>45242.1</v>
+      </c>
+    </row>
+    <row r="48">
       <c r="A48">
         <v>2010</v>
       </c>
       <c r="B48">
-        <v>22411.599999999999</v>
+        <v>19503.9</v>
       </c>
       <c r="C48">
-        <v>1047.48</v>
+        <v>892.471</v>
       </c>
       <c r="D48">
-        <v>20412.599999999999</v>
+        <v>17799.1</v>
       </c>
       <c r="E48">
-        <v>24606.3</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+        <v>21372.1</v>
+      </c>
+    </row>
+    <row r="49">
       <c r="A49">
         <v>2011</v>
       </c>
       <c r="B49">
-        <v>13623.1</v>
+        <v>12210.8</v>
       </c>
       <c r="C49">
-        <v>790.76099999999997</v>
+        <v>698.107</v>
       </c>
       <c r="D49">
-        <v>12131.1</v>
+        <v>10892.4</v>
       </c>
       <c r="E49">
-        <v>15298.6</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+        <v>13688.7</v>
+      </c>
+    </row>
+    <row r="50">
       <c r="A50">
         <v>2012</v>
       </c>
       <c r="B50">
-        <v>11795.6</v>
+        <v>11083</v>
       </c>
       <c r="C50">
-        <v>708.447</v>
+        <v>654.764</v>
       </c>
       <c r="D50">
-        <v>10461.700000000001</v>
+        <v>9848.85</v>
       </c>
       <c r="E50">
-        <v>13299.7</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+        <v>12471.7</v>
+      </c>
+    </row>
+    <row r="51">
       <c r="A51">
         <v>2013</v>
       </c>
       <c r="B51">
-        <v>42753.2</v>
+        <v>40787.1</v>
       </c>
       <c r="C51">
-        <v>1453.31</v>
+        <v>1364.27</v>
       </c>
       <c r="D51">
-        <v>39944</v>
+        <v>38148.5</v>
       </c>
       <c r="E51">
-        <v>45760</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+        <v>43608.1</v>
+      </c>
+    </row>
+    <row r="52">
       <c r="A52">
         <v>2014</v>
       </c>
       <c r="B52">
-        <v>49038.7</v>
+        <v>45620.9</v>
       </c>
       <c r="C52">
-        <v>1801.91</v>
+        <v>1744.87</v>
       </c>
       <c r="D52">
-        <v>45565.3</v>
+        <v>42262.4</v>
       </c>
       <c r="E52">
-        <v>52777</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+        <v>49246.2</v>
+      </c>
+    </row>
+    <row r="53">
       <c r="A53">
         <v>2015</v>
       </c>
       <c r="B53">
-        <v>21229.7</v>
+        <v>18859.1</v>
       </c>
       <c r="C53">
-        <v>1244.28</v>
+        <v>1157.06</v>
       </c>
       <c r="D53">
-        <v>18883.400000000001</v>
+        <v>16683.2</v>
       </c>
       <c r="E53">
-        <v>23867.599999999999</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+        <v>21318.7</v>
+      </c>
+    </row>
+    <row r="54">
       <c r="A54">
         <v>2016</v>
       </c>
       <c r="B54">
-        <v>8015.08</v>
+        <v>6999.46</v>
       </c>
       <c r="C54">
-        <v>816.05799999999999</v>
+        <v>729.74</v>
       </c>
       <c r="D54">
-        <v>6541.84</v>
+        <v>5685.3</v>
       </c>
       <c r="E54">
-        <v>9820.09</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+        <v>8617.4</v>
+      </c>
+    </row>
+    <row r="55">
       <c r="A55">
         <v>2017</v>
       </c>
       <c r="B55">
-        <v>8016.94</v>
+        <v>7236.34</v>
       </c>
       <c r="C55">
-        <v>943.74800000000005</v>
+        <v>873.478</v>
       </c>
       <c r="D55">
-        <v>6340.31</v>
+        <v>5689.22</v>
       </c>
       <c r="E55">
-        <v>10136.9</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+        <v>9204.17</v>
+      </c>
+    </row>
+    <row r="56">
       <c r="A56">
         <v>2018</v>
       </c>
       <c r="B56">
-        <v>16501.8</v>
+        <v>15327.1</v>
       </c>
       <c r="C56">
-        <v>1813.06</v>
+        <v>1721.36</v>
       </c>
       <c r="D56">
-        <v>13255.1</v>
+        <v>12252.2</v>
       </c>
       <c r="E56">
-        <v>20543.599999999999</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+        <v>19173.6</v>
+      </c>
+    </row>
+    <row r="57">
       <c r="A57">
         <v>2019</v>
       </c>
       <c r="B57">
-        <v>81112.7</v>
+        <v>76692.39999999999</v>
       </c>
       <c r="C57">
-        <v>7844.12</v>
+        <v>7515.24</v>
       </c>
       <c r="D57">
-        <v>66878.399999999994</v>
+        <v>63072.6</v>
       </c>
       <c r="E57">
-        <v>98376.5</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+        <v>93253.2</v>
+      </c>
+    </row>
+    <row r="58">
       <c r="A58">
         <v>2020</v>
       </c>
       <c r="B58">
-        <v>20413.7</v>
+        <v>18850.1</v>
       </c>
       <c r="C58">
-        <v>3011.26</v>
+        <v>2783.38</v>
       </c>
       <c r="D58">
-        <v>15222.4</v>
+        <v>14052.4</v>
       </c>
       <c r="E58">
-        <v>27375.4</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+        <v>25285.9</v>
+      </c>
+    </row>
+    <row r="59">
       <c r="A59">
         <v>2021</v>
       </c>
       <c r="B59">
-        <v>11331.5</v>
+        <v>10150.1</v>
       </c>
       <c r="C59">
-        <v>2214.9299999999998</v>
+        <v>2002.65</v>
       </c>
       <c r="D59">
-        <v>7692.98</v>
+        <v>6866.42</v>
       </c>
       <c r="E59">
-        <v>16690.8</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+        <v>15004.2</v>
+      </c>
+    </row>
+    <row r="60">
       <c r="A60">
         <v>2022</v>
       </c>
       <c r="B60">
-        <v>11485.8</v>
+        <v>10251.6</v>
       </c>
       <c r="C60">
-        <v>2862.32</v>
+        <v>2580.31</v>
       </c>
       <c r="D60">
-        <v>7030.01</v>
+        <v>6244.77</v>
       </c>
       <c r="E60">
-        <v>18765.7</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+        <v>16829.3</v>
+      </c>
+    </row>
+    <row r="61">
       <c r="A61">
         <v>2023</v>
       </c>
       <c r="B61">
-        <v>16759.099999999999</v>
+        <v>14309.7</v>
       </c>
       <c r="C61">
-        <v>4906.37</v>
+        <v>4169.05</v>
       </c>
       <c r="D61">
-        <v>9444.4</v>
+        <v>8085.55</v>
       </c>
       <c r="E61">
-        <v>29739.1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+        <v>25325.2</v>
+      </c>
+    </row>
+    <row r="62">
       <c r="A62">
         <v>2024</v>
       </c>
       <c r="B62">
-        <v>18286.099999999999</v>
+        <v>14007.9</v>
       </c>
       <c r="C62">
-        <v>10131.1</v>
+        <v>8300.040000000001</v>
       </c>
       <c r="D62">
-        <v>6497.04</v>
+        <v>4676.33</v>
       </c>
       <c r="E62">
-        <v>51466.5</v>
+        <v>41960.3</v>
       </c>
     </row>
   </sheetData>
@@ -2375,1062 +2126,1072 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83A50ECF-11B9-4587-914A-B2A5116E536F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E62"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Est</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>LB</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>UB</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2">
         <v>1964</v>
       </c>
       <c r="B2">
-        <v>530.36699999999996</v>
+        <v>1609.19</v>
       </c>
       <c r="C2">
-        <v>143.20500000000001</v>
+        <v>239.538</v>
       </c>
       <c r="D2">
-        <v>312.005</v>
+        <v>1196.8</v>
       </c>
       <c r="E2">
-        <v>901.55399999999997</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+        <v>2163.69</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3">
         <v>1965</v>
       </c>
       <c r="B3">
-        <v>621.96900000000005</v>
+        <v>1588.27</v>
       </c>
       <c r="C3">
-        <v>139.828</v>
+        <v>228.06</v>
       </c>
       <c r="D3">
-        <v>398.93299999999999</v>
+        <v>1193.55</v>
       </c>
       <c r="E3">
-        <v>969.702</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+        <v>2113.54</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4">
         <v>1966</v>
       </c>
       <c r="B4">
-        <v>718.678</v>
+        <v>1567.71</v>
       </c>
       <c r="C4">
-        <v>153.01900000000001</v>
+        <v>229.742</v>
       </c>
       <c r="D4">
-        <v>471.67500000000001</v>
+        <v>1171.26</v>
       </c>
       <c r="E4">
-        <v>1095.03</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+        <v>2098.35</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5">
         <v>1967</v>
       </c>
       <c r="B5">
-        <v>903.221</v>
+        <v>1638.03</v>
       </c>
       <c r="C5">
-        <v>172.63</v>
+        <v>240.42</v>
       </c>
       <c r="D5">
-        <v>618.4</v>
+        <v>1223.25</v>
       </c>
       <c r="E5">
-        <v>1319.22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+        <v>2193.46</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6">
         <v>1968</v>
       </c>
       <c r="B6">
-        <v>1120.23</v>
+        <v>1762.89</v>
       </c>
       <c r="C6">
-        <v>214.048</v>
+        <v>275.33</v>
       </c>
       <c r="D6">
-        <v>767.05399999999997</v>
+        <v>1292.36</v>
       </c>
       <c r="E6">
-        <v>1636.01</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+        <v>2404.73</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7">
         <v>1969</v>
       </c>
       <c r="B7">
-        <v>1371.65</v>
+        <v>1957.39</v>
       </c>
       <c r="C7">
-        <v>253.773</v>
+        <v>310.393</v>
       </c>
       <c r="D7">
-        <v>950.37400000000002</v>
+        <v>1428.22</v>
       </c>
       <c r="E7">
-        <v>1979.67</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+        <v>2682.62</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8">
         <v>1970</v>
       </c>
       <c r="B8">
-        <v>1530.53</v>
+        <v>2059.63</v>
       </c>
       <c r="C8">
-        <v>271.64100000000002</v>
+        <v>321.855</v>
       </c>
       <c r="D8">
-        <v>1076.1600000000001</v>
+        <v>1509.64</v>
       </c>
       <c r="E8">
-        <v>2176.7399999999998</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+        <v>2809.99</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9">
         <v>1971</v>
       </c>
       <c r="B9">
-        <v>1673.83</v>
+        <v>2177.41</v>
       </c>
       <c r="C9">
-        <v>291.01400000000001</v>
+        <v>338.869</v>
       </c>
       <c r="D9">
-        <v>1185.28</v>
+        <v>1597.98</v>
       </c>
       <c r="E9">
-        <v>2363.75</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+        <v>2966.95</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10">
         <v>1972</v>
       </c>
       <c r="B10">
-        <v>1590.06</v>
+        <v>2053.93</v>
       </c>
       <c r="C10">
-        <v>271.286</v>
+        <v>318.558</v>
       </c>
       <c r="D10">
-        <v>1133.1400000000001</v>
+        <v>1508.94</v>
       </c>
       <c r="E10">
-        <v>2231.2399999999998</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+        <v>2795.77</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11">
         <v>1973</v>
       </c>
       <c r="B11">
-        <v>1364.05</v>
+        <v>1794.07</v>
       </c>
       <c r="C11">
-        <v>251.64400000000001</v>
+        <v>299.556</v>
       </c>
       <c r="D11">
-        <v>946.08799999999997</v>
+        <v>1287.68</v>
       </c>
       <c r="E11">
-        <v>1966.67</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+        <v>2499.61</v>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12">
         <v>1974</v>
       </c>
       <c r="B12">
-        <v>1026.54</v>
+        <v>1411.82</v>
       </c>
       <c r="C12">
-        <v>221.44800000000001</v>
+        <v>270.825</v>
       </c>
       <c r="D12">
-        <v>670.08100000000002</v>
+        <v>965.303</v>
       </c>
       <c r="E12">
-        <v>1572.62</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+        <v>2064.88</v>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13">
         <v>1975</v>
       </c>
       <c r="B13">
-        <v>966.29200000000003</v>
+        <v>1349.82</v>
       </c>
       <c r="C13">
-        <v>198.541</v>
+        <v>254.586</v>
       </c>
       <c r="D13">
-        <v>643.404</v>
+        <v>928.717</v>
       </c>
       <c r="E13">
-        <v>1451.22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+        <v>1961.86</v>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14">
         <v>1976</v>
       </c>
       <c r="B14">
-        <v>926.93899999999996</v>
+        <v>1290.86</v>
       </c>
       <c r="C14">
-        <v>148.636</v>
+        <v>206.817</v>
       </c>
       <c r="D14">
-        <v>673.99199999999996</v>
+        <v>938.85</v>
       </c>
       <c r="E14">
-        <v>1274.82</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+        <v>1774.84</v>
+      </c>
+    </row>
+    <row r="15">
       <c r="A15">
         <v>1977</v>
       </c>
       <c r="B15">
-        <v>1111.1099999999999</v>
+        <v>1551.78</v>
       </c>
       <c r="C15">
-        <v>145.911</v>
+        <v>219.697</v>
       </c>
       <c r="D15">
-        <v>855.42</v>
+        <v>1170.76</v>
       </c>
       <c r="E15">
-        <v>1443.22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+        <v>2056.81</v>
+      </c>
+    </row>
+    <row r="16">
       <c r="A16">
         <v>1978</v>
       </c>
       <c r="B16">
-        <v>989.91700000000003</v>
+        <v>1445.12</v>
       </c>
       <c r="C16">
-        <v>119.124</v>
+        <v>197.255</v>
       </c>
       <c r="D16">
-        <v>778.84500000000003</v>
+        <v>1101.26</v>
       </c>
       <c r="E16">
-        <v>1258.19</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+        <v>1896.34</v>
+      </c>
+    </row>
+    <row r="17">
       <c r="A17">
         <v>1979</v>
       </c>
       <c r="B17">
-        <v>906.76099999999997</v>
+        <v>1414.65</v>
       </c>
       <c r="C17">
-        <v>101.512</v>
+        <v>182.959</v>
       </c>
       <c r="D17">
-        <v>725.36500000000001</v>
+        <v>1093.4</v>
       </c>
       <c r="E17">
-        <v>1133.52</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+        <v>1830.29</v>
+      </c>
+    </row>
+    <row r="18">
       <c r="A18">
         <v>1980</v>
       </c>
       <c r="B18">
-        <v>1071.6199999999999</v>
+        <v>1748.01</v>
       </c>
       <c r="C18">
-        <v>98.727500000000006</v>
+        <v>189.584</v>
       </c>
       <c r="D18">
-        <v>891.63800000000003</v>
+        <v>1408.03</v>
       </c>
       <c r="E18">
-        <v>1287.94</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+        <v>2170.06</v>
+      </c>
+    </row>
+    <row r="19">
       <c r="A19">
         <v>1981</v>
       </c>
       <c r="B19">
-        <v>1653.19</v>
+        <v>2580.19</v>
       </c>
       <c r="C19">
-        <v>104.78100000000001</v>
+        <v>201.521</v>
       </c>
       <c r="D19">
-        <v>1456.55</v>
+        <v>2207.57</v>
       </c>
       <c r="E19">
-        <v>1876.38</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+        <v>3015.7</v>
+      </c>
+    </row>
+    <row r="20">
       <c r="A20">
         <v>1982</v>
       </c>
       <c r="B20">
-        <v>2310.31</v>
+        <v>3390.52</v>
       </c>
       <c r="C20">
-        <v>129.68199999999999</v>
+        <v>223.595</v>
       </c>
       <c r="D20">
-        <v>2065.16</v>
+        <v>2971.99</v>
       </c>
       <c r="E20">
-        <v>2584.5700000000002</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+        <v>3867.99</v>
+      </c>
+    </row>
+    <row r="21">
       <c r="A21">
         <v>1983</v>
       </c>
       <c r="B21">
-        <v>3121.24</v>
+        <v>4270.84</v>
       </c>
       <c r="C21">
-        <v>170.149</v>
+        <v>258.545</v>
       </c>
       <c r="D21">
-        <v>2799.06</v>
+        <v>3784.25</v>
       </c>
       <c r="E21">
-        <v>3480.5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+        <v>4820.01</v>
+      </c>
+    </row>
+    <row r="22">
       <c r="A22">
         <v>1984</v>
       </c>
       <c r="B22">
-        <v>3252.82</v>
+        <v>4226.79</v>
       </c>
       <c r="C22">
-        <v>176.87</v>
+        <v>244.922</v>
       </c>
       <c r="D22">
-        <v>2917.87</v>
+        <v>3764.63</v>
       </c>
       <c r="E22">
-        <v>3626.22</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+        <v>4745.69</v>
+      </c>
+    </row>
+    <row r="23">
       <c r="A23">
         <v>1985</v>
       </c>
       <c r="B23">
-        <v>3778.9</v>
+        <v>4550.68</v>
       </c>
       <c r="C23">
-        <v>181.45</v>
+        <v>232.075</v>
       </c>
       <c r="D23">
-        <v>3433.07</v>
+        <v>4109.69</v>
       </c>
       <c r="E23">
-        <v>4159.57</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+        <v>5038.99</v>
+      </c>
+    </row>
+    <row r="24">
       <c r="A24">
         <v>1986</v>
       </c>
       <c r="B24">
-        <v>3727.19</v>
+        <v>4245.34</v>
       </c>
       <c r="C24">
-        <v>163.16300000000001</v>
+        <v>197.807</v>
       </c>
       <c r="D24">
-        <v>3414.89</v>
+        <v>3867.8</v>
       </c>
       <c r="E24">
-        <v>4068.06</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+        <v>4659.74</v>
+      </c>
+    </row>
+    <row r="25">
       <c r="A25">
         <v>1987</v>
       </c>
       <c r="B25">
-        <v>3794.67</v>
+        <v>4121.86</v>
       </c>
       <c r="C25">
-        <v>143.81299999999999</v>
+        <v>171.464</v>
       </c>
       <c r="D25">
-        <v>3517.77</v>
+        <v>3792.95</v>
       </c>
       <c r="E25">
-        <v>4093.37</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+        <v>4479.3</v>
+      </c>
+    </row>
+    <row r="26">
       <c r="A26">
         <v>1988</v>
       </c>
       <c r="B26">
-        <v>3607.06</v>
+        <v>3802.13</v>
       </c>
       <c r="C26">
-        <v>119.76</v>
+        <v>145.09</v>
       </c>
       <c r="D26">
-        <v>3375.38</v>
+        <v>3522.84</v>
       </c>
       <c r="E26">
-        <v>3854.64</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+        <v>4103.56</v>
+      </c>
+    </row>
+    <row r="27">
       <c r="A27">
         <v>1989</v>
       </c>
       <c r="B27">
-        <v>3130.6</v>
+        <v>3233.94</v>
       </c>
       <c r="C27">
-        <v>102.541</v>
+        <v>125.291</v>
       </c>
       <c r="D27">
-        <v>2932.14</v>
+        <v>2992.91</v>
       </c>
       <c r="E27">
-        <v>3342.48</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+        <v>3494.39</v>
+      </c>
+    </row>
+    <row r="28">
       <c r="A28">
         <v>1990</v>
       </c>
       <c r="B28">
-        <v>2648.47</v>
+        <v>2695.22</v>
       </c>
       <c r="C28">
-        <v>92.520200000000003</v>
+        <v>113.888</v>
       </c>
       <c r="D28">
-        <v>2469.8000000000002</v>
+        <v>2476.9</v>
       </c>
       <c r="E28">
-        <v>2840.07</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+        <v>2932.79</v>
+      </c>
+    </row>
+    <row r="29">
       <c r="A29">
         <v>1991</v>
       </c>
       <c r="B29">
-        <v>2119.04</v>
+        <v>2133.48</v>
       </c>
       <c r="C29">
-        <v>83.238600000000005</v>
+        <v>103.735</v>
       </c>
       <c r="D29">
-        <v>1958.99</v>
+        <v>1935.89</v>
       </c>
       <c r="E29">
-        <v>2292.16</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+        <v>2351.24</v>
+      </c>
+    </row>
+    <row r="30">
       <c r="A30">
         <v>1992</v>
       </c>
       <c r="B30">
-        <v>2019.33</v>
+        <v>2031</v>
       </c>
       <c r="C30">
-        <v>71.266000000000005</v>
+        <v>89.65779999999999</v>
       </c>
       <c r="D30">
-        <v>1881.76</v>
+        <v>1859.45</v>
       </c>
       <c r="E30">
-        <v>2166.9699999999998</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+        <v>2218.37</v>
+      </c>
+    </row>
+    <row r="31">
       <c r="A31">
         <v>1993</v>
       </c>
       <c r="B31">
-        <v>2682.09</v>
+        <v>2715.17</v>
       </c>
       <c r="C31">
-        <v>82.069699999999997</v>
+        <v>98.50239999999999</v>
       </c>
       <c r="D31">
-        <v>2522.91</v>
+        <v>2525.2</v>
       </c>
       <c r="E31">
-        <v>2851.31</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+        <v>2919.43</v>
+      </c>
+    </row>
+    <row r="32">
       <c r="A32">
         <v>1994</v>
       </c>
       <c r="B32">
-        <v>3127.23</v>
+        <v>3186.78</v>
       </c>
       <c r="C32">
-        <v>93.923100000000005</v>
+        <v>109.373</v>
       </c>
       <c r="D32">
-        <v>2944.96</v>
+        <v>2975.43</v>
       </c>
       <c r="E32">
-        <v>3320.79</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+        <v>3413.14</v>
+      </c>
+    </row>
+    <row r="33">
       <c r="A33">
         <v>1995</v>
       </c>
       <c r="B33">
-        <v>3344.74</v>
+        <v>3426.17</v>
       </c>
       <c r="C33">
-        <v>97.742099999999994</v>
+        <v>113.582</v>
       </c>
       <c r="D33">
-        <v>3154.9</v>
+        <v>3206.43</v>
       </c>
       <c r="E33">
-        <v>3546.01</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+        <v>3660.97</v>
+      </c>
+    </row>
+    <row r="34">
       <c r="A34">
         <v>1996</v>
       </c>
       <c r="B34">
-        <v>3282.19</v>
+        <v>3375.67</v>
       </c>
       <c r="C34">
-        <v>96.314800000000005</v>
+        <v>112.568</v>
       </c>
       <c r="D34">
-        <v>3095.15</v>
+        <v>3157.94</v>
       </c>
       <c r="E34">
-        <v>3480.54</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+        <v>3608.42</v>
+      </c>
+    </row>
+    <row r="35">
       <c r="A35">
         <v>1997</v>
       </c>
       <c r="B35">
-        <v>3185.41</v>
+        <v>3287.41</v>
       </c>
       <c r="C35">
-        <v>96.719200000000001</v>
+        <v>113.371</v>
       </c>
       <c r="D35">
-        <v>2997.77</v>
+        <v>3068.37</v>
       </c>
       <c r="E35">
-        <v>3384.79</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+        <v>3522.08</v>
+      </c>
+    </row>
+    <row r="36">
       <c r="A36">
         <v>1998</v>
       </c>
       <c r="B36">
-        <v>2699.72</v>
+        <v>2797.45</v>
       </c>
       <c r="C36">
-        <v>83.568600000000004</v>
+        <v>98.3604</v>
       </c>
       <c r="D36">
-        <v>2537.69</v>
+        <v>2607.55</v>
       </c>
       <c r="E36">
-        <v>2872.1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+        <v>3001.19</v>
+      </c>
+    </row>
+    <row r="37">
       <c r="A37">
         <v>1999</v>
       </c>
       <c r="B37">
-        <v>2821.77</v>
+        <v>2932.43</v>
       </c>
       <c r="C37">
-        <v>82.914100000000005</v>
+        <v>97.08410000000001</v>
       </c>
       <c r="D37">
-        <v>2660.75</v>
+        <v>2744.6</v>
       </c>
       <c r="E37">
-        <v>2992.53</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+        <v>3133.11</v>
+      </c>
+    </row>
+    <row r="38">
       <c r="A38">
         <v>2000</v>
       </c>
       <c r="B38">
-        <v>2722.38</v>
+        <v>2838.76</v>
       </c>
       <c r="C38">
-        <v>77.702299999999994</v>
+        <v>90.184</v>
       </c>
       <c r="D38">
-        <v>2571.36</v>
+        <v>2664.05</v>
       </c>
       <c r="E38">
-        <v>2882.27</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+        <v>3024.94</v>
+      </c>
+    </row>
+    <row r="39">
       <c r="A39">
         <v>2001</v>
       </c>
       <c r="B39">
-        <v>2762.51</v>
+        <v>2896.24</v>
       </c>
       <c r="C39">
-        <v>79.018199999999993</v>
+        <v>91.0082</v>
       </c>
       <c r="D39">
-        <v>2608.94</v>
+        <v>2719.86</v>
       </c>
       <c r="E39">
-        <v>2925.12</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+        <v>3084.05</v>
+      </c>
+    </row>
+    <row r="40">
       <c r="A40">
         <v>2002</v>
       </c>
       <c r="B40">
-        <v>2566.4299999999998</v>
+        <v>2708.8</v>
       </c>
       <c r="C40">
-        <v>73.337000000000003</v>
+        <v>84.4092</v>
       </c>
       <c r="D40">
-        <v>2423.9</v>
+        <v>2545.18</v>
       </c>
       <c r="E40">
-        <v>2717.35</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+        <v>2882.95</v>
+      </c>
+    </row>
+    <row r="41">
       <c r="A41">
         <v>2003</v>
       </c>
       <c r="B41">
-        <v>2602.8000000000002</v>
+        <v>2750.68</v>
       </c>
       <c r="C41">
-        <v>69.499300000000005</v>
+        <v>79.1965</v>
       </c>
       <c r="D41">
-        <v>2467.4699999999998</v>
+        <v>2596.79</v>
       </c>
       <c r="E41">
-        <v>2745.55</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+        <v>2913.69</v>
+      </c>
+    </row>
+    <row r="42">
       <c r="A42">
         <v>2004</v>
       </c>
       <c r="B42">
-        <v>2898.55</v>
+        <v>3053.73</v>
       </c>
       <c r="C42">
-        <v>73.181799999999996</v>
+        <v>81.5817</v>
       </c>
       <c r="D42">
-        <v>2755.84</v>
+        <v>2894.88</v>
       </c>
       <c r="E42">
-        <v>3048.65</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+        <v>3221.3</v>
+      </c>
+    </row>
+    <row r="43">
       <c r="A43">
         <v>2005</v>
       </c>
       <c r="B43">
-        <v>2551.29</v>
+        <v>2690.83</v>
       </c>
       <c r="C43">
-        <v>65.499399999999994</v>
+        <v>72.6825</v>
       </c>
       <c r="D43">
-        <v>2423.62</v>
+        <v>2549.35</v>
       </c>
       <c r="E43">
-        <v>2685.69</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+        <v>2840.17</v>
+      </c>
+    </row>
+    <row r="44">
       <c r="A44">
         <v>2006</v>
       </c>
       <c r="B44">
-        <v>2326.13</v>
+        <v>2459.9</v>
       </c>
       <c r="C44">
-        <v>62.856499999999997</v>
+        <v>70.1341</v>
       </c>
       <c r="D44">
-        <v>2203.77</v>
+        <v>2323.58</v>
       </c>
       <c r="E44">
-        <v>2455.27</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+        <v>2604.21</v>
+      </c>
+    </row>
+    <row r="45">
       <c r="A45">
         <v>2007</v>
       </c>
       <c r="B45">
-        <v>1893.64</v>
+        <v>2012.25</v>
       </c>
       <c r="C45">
-        <v>56.907600000000002</v>
+        <v>64.46550000000001</v>
       </c>
       <c r="D45">
-        <v>1783.2</v>
+        <v>1887.39</v>
       </c>
       <c r="E45">
-        <v>2010.92</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+        <v>2145.37</v>
+      </c>
+    </row>
+    <row r="46">
       <c r="A46">
         <v>2008</v>
       </c>
       <c r="B46">
-        <v>1432.93</v>
+        <v>1522.86</v>
       </c>
       <c r="C46">
-        <v>48.224400000000003</v>
+        <v>55.4351</v>
       </c>
       <c r="D46">
-        <v>1339.68</v>
+        <v>1415.96</v>
       </c>
       <c r="E46">
-        <v>1532.66</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+        <v>1637.82</v>
+      </c>
+    </row>
+    <row r="47">
       <c r="A47">
         <v>2009</v>
       </c>
       <c r="B47">
-        <v>1515.44</v>
+        <v>1556.95</v>
       </c>
       <c r="C47">
-        <v>49.628799999999998</v>
+        <v>54.738</v>
       </c>
       <c r="D47">
-        <v>1419.39</v>
+        <v>1451.27</v>
       </c>
       <c r="E47">
-        <v>1617.99</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+        <v>1670.33</v>
+      </c>
+    </row>
+    <row r="48">
       <c r="A48">
         <v>2010</v>
       </c>
       <c r="B48">
-        <v>1554.75</v>
+        <v>1531.05</v>
       </c>
       <c r="C48">
-        <v>50.253900000000002</v>
+        <v>50.9489</v>
       </c>
       <c r="D48">
-        <v>1457.45</v>
+        <v>1432.49</v>
       </c>
       <c r="E48">
-        <v>1658.55</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+        <v>1636.38</v>
+      </c>
+    </row>
+    <row r="49">
       <c r="A49">
         <v>2011</v>
       </c>
       <c r="B49">
-        <v>1916.05</v>
+        <v>1781.05</v>
       </c>
       <c r="C49">
-        <v>57.997399999999999</v>
+        <v>53.083</v>
       </c>
       <c r="D49">
-        <v>1803.52</v>
+        <v>1678</v>
       </c>
       <c r="E49">
-        <v>2035.6</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+        <v>1890.42</v>
+      </c>
+    </row>
+    <row r="50">
       <c r="A50">
         <v>2012</v>
       </c>
       <c r="B50">
-        <v>2345.9899999999998</v>
+        <v>2070.23</v>
       </c>
       <c r="C50">
-        <v>69.203999999999994</v>
+        <v>59.2069</v>
       </c>
       <c r="D50">
-        <v>2211.62</v>
+        <v>1955.16</v>
       </c>
       <c r="E50">
-        <v>2488.5300000000002</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+        <v>2192.07</v>
+      </c>
+    </row>
+    <row r="51">
       <c r="A51">
         <v>2013</v>
       </c>
       <c r="B51">
-        <v>2675.43</v>
+        <v>2279.82</v>
       </c>
       <c r="C51">
-        <v>81.986199999999997</v>
+        <v>68.369</v>
       </c>
       <c r="D51">
-        <v>2516.42</v>
+        <v>2147.13</v>
       </c>
       <c r="E51">
-        <v>2844.49</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+        <v>2420.71</v>
+      </c>
+    </row>
+    <row r="52">
       <c r="A52">
         <v>2014</v>
       </c>
       <c r="B52">
-        <v>2620.0500000000002</v>
+        <v>2174.75</v>
       </c>
       <c r="C52">
-        <v>86.319100000000006</v>
+        <v>70.9499</v>
       </c>
       <c r="D52">
-        <v>2453.02</v>
+        <v>2037.41</v>
       </c>
       <c r="E52">
-        <v>2798.46</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+        <v>2321.34</v>
+      </c>
+    </row>
+    <row r="53">
       <c r="A53">
         <v>2015</v>
       </c>
       <c r="B53">
-        <v>2447.87</v>
+        <v>2043.53</v>
       </c>
       <c r="C53">
-        <v>79.449200000000005</v>
+        <v>65.0817</v>
       </c>
       <c r="D53">
-        <v>2294.06</v>
+        <v>1917.46</v>
       </c>
       <c r="E53">
-        <v>2612</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+        <v>2177.9</v>
+      </c>
+    </row>
+    <row r="54">
       <c r="A54">
         <v>2016</v>
       </c>
       <c r="B54">
-        <v>2716.45</v>
+        <v>2330.86</v>
       </c>
       <c r="C54">
-        <v>83.483900000000006</v>
+        <v>71.304</v>
       </c>
       <c r="D54">
-        <v>2554.5500000000002</v>
+        <v>2192.56</v>
       </c>
       <c r="E54">
-        <v>2888.62</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+        <v>2477.89</v>
+      </c>
+    </row>
+    <row r="55">
       <c r="A55">
         <v>2017</v>
       </c>
       <c r="B55">
-        <v>3165.77</v>
+        <v>2753.75</v>
       </c>
       <c r="C55">
-        <v>99.532499999999999</v>
+        <v>90.8935</v>
       </c>
       <c r="D55">
-        <v>2972.88</v>
+        <v>2577.88</v>
       </c>
       <c r="E55">
-        <v>3371.18</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+        <v>2941.62</v>
+      </c>
+    </row>
+    <row r="56">
       <c r="A56">
         <v>2018</v>
       </c>
       <c r="B56">
-        <v>3025.99</v>
+        <v>2615.71</v>
       </c>
       <c r="C56">
-        <v>105.952</v>
+        <v>100.941</v>
       </c>
       <c r="D56">
-        <v>2821.4</v>
+        <v>2421.49</v>
       </c>
       <c r="E56">
-        <v>3245.42</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+        <v>2825.51</v>
+      </c>
+    </row>
+    <row r="57">
       <c r="A57">
         <v>2019</v>
       </c>
       <c r="B57">
-        <v>2938.37</v>
+        <v>2496.08</v>
       </c>
       <c r="C57">
-        <v>121.59699999999999</v>
+        <v>119.928</v>
       </c>
       <c r="D57">
-        <v>2705.06</v>
+        <v>2267.52</v>
       </c>
       <c r="E57">
-        <v>3191.8</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+        <v>2747.69</v>
+      </c>
+    </row>
+    <row r="58">
       <c r="A58">
         <v>2020</v>
       </c>
       <c r="B58">
-        <v>2258.9</v>
+        <v>1872.4</v>
       </c>
       <c r="C58">
-        <v>116.36</v>
+        <v>117.28</v>
       </c>
       <c r="D58">
-        <v>2037.91</v>
+        <v>1652.14</v>
       </c>
       <c r="E58">
-        <v>2503.86</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+        <v>2122.02</v>
+      </c>
+    </row>
+    <row r="59">
       <c r="A59">
         <v>2021</v>
       </c>
       <c r="B59">
-        <v>2464.21</v>
+        <v>2097.48</v>
       </c>
       <c r="C59">
-        <v>166.96199999999999</v>
+        <v>169.074</v>
       </c>
       <c r="D59">
-        <v>2152.2600000000002</v>
+        <v>1785.65</v>
       </c>
       <c r="E59">
-        <v>2821.38</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+        <v>2463.77</v>
+      </c>
+    </row>
+    <row r="60">
       <c r="A60">
         <v>2022</v>
       </c>
       <c r="B60">
-        <v>3406.88</v>
+        <v>2993.88</v>
       </c>
       <c r="C60">
-        <v>295.98099999999999</v>
+        <v>292.879</v>
       </c>
       <c r="D60">
-        <v>2864.43</v>
+        <v>2463.01</v>
       </c>
       <c r="E60">
-        <v>4052.06</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+        <v>3639.17</v>
+      </c>
+    </row>
+    <row r="61">
       <c r="A61">
         <v>2023</v>
       </c>
       <c r="B61">
-        <v>3333.76</v>
+        <v>2934.81</v>
       </c>
       <c r="C61">
-        <v>338.84300000000002</v>
+        <v>332.14</v>
       </c>
       <c r="D61">
-        <v>2721.94</v>
+        <v>2342.03</v>
       </c>
       <c r="E61">
-        <v>4083.11</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+        <v>3677.63</v>
+      </c>
+    </row>
+    <row r="62">
       <c r="A62">
         <v>2024</v>
       </c>
       <c r="B62">
-        <v>3389.48</v>
+        <v>2951.42</v>
       </c>
       <c r="C62">
-        <v>408.52199999999999</v>
+        <v>397.91</v>
       </c>
       <c r="D62">
-        <v>2665.77</v>
+        <v>2256.6</v>
       </c>
       <c r="E62">
-        <v>4309.67</v>
+        <v>3860.17</v>
       </c>
     </row>
   </sheetData>
@@ -3439,25 +3200,560 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D96C36B5-E914-416F-81DC-A3B7F75C1F46}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E1" t="s">
-        <v>6</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Est</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>LB</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>UB</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E62"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Est</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>LB</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>UB</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>1964</v>
+      </c>
+      <c r="B2">
+        <v>5641.81275728447</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>1965</v>
+      </c>
+      <c r="B3">
+        <v>5865.825615022593</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>1966</v>
+      </c>
+      <c r="B4">
+        <v>5961.022848637646</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>1967</v>
+      </c>
+      <c r="B5">
+        <v>6580.459711195219</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>1968</v>
+      </c>
+      <c r="B6">
+        <v>7116.503853813798</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>1969</v>
+      </c>
+      <c r="B7">
+        <v>7650.999442761527</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>1970</v>
+      </c>
+      <c r="B8">
+        <v>8319.008467788655</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>1971</v>
+      </c>
+      <c r="B9">
+        <v>8254.461477212497</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>1972</v>
+      </c>
+      <c r="B10">
+        <v>7552.301458332855</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>1973</v>
+      </c>
+      <c r="B11">
+        <v>6855.70920865673</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>1974</v>
+      </c>
+      <c r="B12">
+        <v>5888.675815111676</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>1975</v>
+      </c>
+      <c r="B13">
+        <v>5197.344113528823</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>1976</v>
+      </c>
+      <c r="B14">
+        <v>4876.346871371911</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>1977</v>
+      </c>
+      <c r="B15">
+        <v>4733.017238790893</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>1978</v>
+      </c>
+      <c r="B16">
+        <v>5230.010501770162</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>1979</v>
+      </c>
+      <c r="B17">
+        <v>6774.335080023299</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>1980</v>
+      </c>
+      <c r="B18">
+        <v>7667.687728460764</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>1981</v>
+      </c>
+      <c r="B19">
+        <v>9326.256894073582</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>1982</v>
+      </c>
+      <c r="B20">
+        <v>11020.19997519719</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>1983</v>
+      </c>
+      <c r="B21">
+        <v>12000.04368709294</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>1984</v>
+      </c>
+      <c r="B22">
+        <v>11405.72271448225</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>1985</v>
+      </c>
+      <c r="B23">
+        <v>12939.01030911007</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>1986</v>
+      </c>
+      <c r="B24">
+        <v>11431.94623395861</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>1987</v>
+      </c>
+      <c r="B25">
+        <v>10616.50944833932</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>1988</v>
+      </c>
+      <c r="B26">
+        <v>9437.542471766257</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>1989</v>
+      </c>
+      <c r="B27">
+        <v>7903.287329967987</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>1990</v>
+      </c>
+      <c r="B28">
+        <v>7530.658170694077</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>1991</v>
+      </c>
+      <c r="B29">
+        <v>8600.141723087716</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>1992</v>
+      </c>
+      <c r="B30">
+        <v>9509.989112830001</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>1993</v>
+      </c>
+      <c r="B31">
+        <v>10123.2478375419</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>1994</v>
+      </c>
+      <c r="B32">
+        <v>10329.38348427103</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>1995</v>
+      </c>
+      <c r="B33">
+        <v>8642.409533508653</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>1996</v>
+      </c>
+      <c r="B34">
+        <v>9057.07149576492</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>1997</v>
+      </c>
+      <c r="B35">
+        <v>8480.700826552235</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>1998</v>
+      </c>
+      <c r="B36">
+        <v>8668.605875463329</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>1999</v>
+      </c>
+      <c r="B37">
+        <v>8775.808486986663</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>2000</v>
+      </c>
+      <c r="B38">
+        <v>9147.449724146605</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>2001</v>
+      </c>
+      <c r="B39">
+        <v>9040.418582098211</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>2002</v>
+      </c>
+      <c r="B40">
+        <v>9529.20228151972</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>2003</v>
+      </c>
+      <c r="B41">
+        <v>10852.80933822908</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>2004</v>
+      </c>
+      <c r="B42">
+        <v>10038.93682182038</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>2005</v>
+      </c>
+      <c r="B43">
+        <v>8276.618885595324</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>2006</v>
+      </c>
+      <c r="B44">
+        <v>6972.698910644904</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>2007</v>
+      </c>
+      <c r="B45">
+        <v>6303.658929037115</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>2008</v>
+      </c>
+      <c r="B46">
+        <v>4883.959992513856</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>2009</v>
+      </c>
+      <c r="B47">
+        <v>5609.100796355677</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>2010</v>
+      </c>
+      <c r="B48">
+        <v>7104.271862259056</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>2011</v>
+      </c>
+      <c r="B49">
+        <v>7612.082186750861</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>2012</v>
+      </c>
+      <c r="B50">
+        <v>7515.449674120482</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>2013</v>
+      </c>
+      <c r="B51">
+        <v>8043.737138306061</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>2014</v>
+      </c>
+      <c r="B52">
+        <v>8812.831445849477</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>2015</v>
+      </c>
+      <c r="B53">
+        <v>9885.103008406117</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>2016</v>
+      </c>
+      <c r="B54">
+        <v>10931.45813478464</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>2017</v>
+      </c>
+      <c r="B55">
+        <v>10064.41568835162</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>2018</v>
+      </c>
+      <c r="B56">
+        <v>8643.791774988584</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>2019</v>
+      </c>
+      <c r="B57">
+        <v>9272.435723300174</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>2020</v>
+      </c>
+      <c r="B58">
+        <v>9870.472409740858</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>2021</v>
+      </c>
+      <c r="B59">
+        <v>9637.040406154458</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>2022</v>
+      </c>
+      <c r="B60">
+        <v>10575.51151871456</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>2023</v>
+      </c>
+      <c r="B61">
+        <v>9435.70847270326</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>2024</v>
+      </c>
+      <c r="B62">
+        <v>8325.603363674047</v>
       </c>
     </row>
   </sheetData>
